--- a/documentAPI.xlsx
+++ b/documentAPI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my-project\shop-backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B097295-99A0-4FB1-8BDC-B2354F349820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0251636-FA5E-4B36-926F-9C1D56FED9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="50">
   <si>
     <t>Error Code</t>
   </si>
@@ -157,6 +157,24 @@
   </si>
   <si>
     <t>The user information not found when login</t>
+  </si>
+  <si>
+    <t>/user-verification</t>
+  </si>
+  <si>
+    <t>E4002</t>
+  </si>
+  <si>
+    <t>The user already authenticated</t>
+  </si>
+  <si>
+    <t>E8002</t>
+  </si>
+  <si>
+    <t>Error when generate verification code!</t>
+  </si>
+  <si>
+    <t>Error when update verification code in database</t>
   </si>
 </sst>
 </file>
@@ -260,17 +278,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
@@ -290,10 +302,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -583,120 +601,120 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
+      <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
+      <c r="T2" s="15"/>
+      <c r="U2" s="15"/>
+      <c r="V2" s="15"/>
+      <c r="W2" s="15"/>
+      <c r="X2" s="15"/>
+      <c r="Y2" s="15"/>
     </row>
     <row r="3" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
-      <c r="V3" s="4"/>
-      <c r="W3" s="4"/>
-      <c r="X3" s="4"/>
-      <c r="Y3" s="4"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="15"/>
+      <c r="O3" s="15"/>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="15"/>
+      <c r="R3" s="15"/>
+      <c r="S3" s="15"/>
+      <c r="T3" s="15"/>
+      <c r="U3" s="15"/>
+      <c r="V3" s="15"/>
+      <c r="W3" s="15"/>
+      <c r="X3" s="15"/>
+      <c r="Y3" s="15"/>
     </row>
     <row r="4" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
-      <c r="V4" s="4"/>
-      <c r="W4" s="4"/>
-      <c r="X4" s="4"/>
-      <c r="Y4" s="4"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15"/>
+      <c r="R4" s="15"/>
+      <c r="S4" s="15"/>
+      <c r="T4" s="15"/>
+      <c r="U4" s="15"/>
+      <c r="V4" s="15"/>
+      <c r="W4" s="15"/>
+      <c r="X4" s="15"/>
+      <c r="Y4" s="15"/>
     </row>
     <row r="6" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="5" t="s">
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="H6" s="7"/>
-      <c r="I6" s="5" t="s">
+      <c r="H6" s="13"/>
+      <c r="I6" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="J6" s="7"/>
-      <c r="K6" s="5" t="s">
+      <c r="J6" s="13"/>
+      <c r="K6" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="5" t="s">
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="R6" s="6"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="6"/>
-      <c r="Y6" s="7"/>
+      <c r="R6" s="14"/>
+      <c r="S6" s="14"/>
+      <c r="T6" s="14"/>
+      <c r="U6" s="14"/>
+      <c r="V6" s="14"/>
+      <c r="W6" s="14"/>
+      <c r="X6" s="14"/>
+      <c r="Y6" s="13"/>
     </row>
     <row r="7" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
@@ -706,29 +724,29 @@
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="3"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="14" t="s">
+      <c r="G7" s="4"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="15"/>
-      <c r="K7" s="8" t="s">
+      <c r="J7" s="5"/>
+      <c r="K7" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="10"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="9"/>
-      <c r="S7" s="9"/>
-      <c r="T7" s="9"/>
-      <c r="U7" s="9"/>
-      <c r="V7" s="9"/>
-      <c r="W7" s="9"/>
-      <c r="X7" s="9"/>
-      <c r="Y7" s="10"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="7"/>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="8"/>
     </row>
     <row r="8" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B8" s="1"/>
@@ -736,31 +754,31 @@
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="3"/>
-      <c r="G8" s="14">
+      <c r="G8" s="4">
         <v>400</v>
       </c>
-      <c r="H8" s="15"/>
-      <c r="I8" s="14" t="s">
+      <c r="H8" s="5"/>
+      <c r="I8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J8" s="15"/>
-      <c r="K8" s="8" t="s">
+      <c r="J8" s="5"/>
+      <c r="K8" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
-      <c r="P8" s="10"/>
-      <c r="Q8" s="8"/>
-      <c r="R8" s="9"/>
-      <c r="S8" s="9"/>
-      <c r="T8" s="9"/>
-      <c r="U8" s="9"/>
-      <c r="V8" s="9"/>
-      <c r="W8" s="9"/>
-      <c r="X8" s="9"/>
-      <c r="Y8" s="10"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="6"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="7"/>
+      <c r="X8" s="7"/>
+      <c r="Y8" s="8"/>
     </row>
     <row r="9" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B9" s="1"/>
@@ -768,33 +786,33 @@
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="3"/>
-      <c r="G9" s="14">
+      <c r="G9" s="4">
         <v>401</v>
       </c>
-      <c r="H9" s="15"/>
-      <c r="I9" s="14" t="s">
+      <c r="H9" s="5"/>
+      <c r="I9" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="J9" s="15"/>
-      <c r="K9" s="8" t="s">
+      <c r="J9" s="5"/>
+      <c r="K9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="10"/>
-      <c r="Q9" s="8" t="s">
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="R9" s="9"/>
-      <c r="S9" s="9"/>
-      <c r="T9" s="9"/>
-      <c r="U9" s="9"/>
-      <c r="V9" s="9"/>
-      <c r="W9" s="9"/>
-      <c r="X9" s="9"/>
-      <c r="Y9" s="10"/>
+      <c r="R9" s="7"/>
+      <c r="S9" s="7"/>
+      <c r="T9" s="7"/>
+      <c r="U9" s="7"/>
+      <c r="V9" s="7"/>
+      <c r="W9" s="7"/>
+      <c r="X9" s="7"/>
+      <c r="Y9" s="8"/>
     </row>
     <row r="10" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B10" s="1"/>
@@ -802,33 +820,33 @@
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="3"/>
-      <c r="G10" s="14">
+      <c r="G10" s="4">
         <v>400</v>
       </c>
-      <c r="H10" s="15"/>
-      <c r="I10" s="14" t="s">
+      <c r="H10" s="5"/>
+      <c r="I10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="J10" s="15"/>
-      <c r="K10" s="8" t="s">
+      <c r="J10" s="5"/>
+      <c r="K10" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="10"/>
-      <c r="Q10" s="8" t="s">
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="R10" s="9"/>
-      <c r="S10" s="9"/>
-      <c r="T10" s="9"/>
-      <c r="U10" s="9"/>
-      <c r="V10" s="9"/>
-      <c r="W10" s="9"/>
-      <c r="X10" s="9"/>
-      <c r="Y10" s="10"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
+      <c r="U10" s="7"/>
+      <c r="V10" s="7"/>
+      <c r="W10" s="7"/>
+      <c r="X10" s="7"/>
+      <c r="Y10" s="8"/>
     </row>
     <row r="11" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B11" s="1"/>
@@ -836,33 +854,33 @@
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="3"/>
-      <c r="G11" s="14">
+      <c r="G11" s="4">
         <v>400</v>
       </c>
-      <c r="H11" s="15"/>
-      <c r="I11" s="14" t="s">
+      <c r="H11" s="5"/>
+      <c r="I11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J11" s="15"/>
-      <c r="K11" s="8" t="s">
+      <c r="J11" s="5"/>
+      <c r="K11" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="10"/>
-      <c r="Q11" s="8" t="s">
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="8"/>
+      <c r="Q11" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="R11" s="9"/>
-      <c r="S11" s="9"/>
-      <c r="T11" s="9"/>
-      <c r="U11" s="9"/>
-      <c r="V11" s="9"/>
-      <c r="W11" s="9"/>
-      <c r="X11" s="9"/>
-      <c r="Y11" s="10"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="7"/>
+      <c r="W11" s="7"/>
+      <c r="X11" s="7"/>
+      <c r="Y11" s="8"/>
     </row>
     <row r="12" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B12" s="1"/>
@@ -870,33 +888,33 @@
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="3"/>
-      <c r="G12" s="14">
+      <c r="G12" s="4">
         <v>400</v>
       </c>
-      <c r="H12" s="15"/>
-      <c r="I12" s="14" t="s">
+      <c r="H12" s="5"/>
+      <c r="I12" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J12" s="15"/>
-      <c r="K12" s="8" t="s">
+      <c r="J12" s="5"/>
+      <c r="K12" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-      <c r="P12" s="10"/>
-      <c r="Q12" s="8" t="s">
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="R12" s="9"/>
-      <c r="S12" s="9"/>
-      <c r="T12" s="9"/>
-      <c r="U12" s="9"/>
-      <c r="V12" s="9"/>
-      <c r="W12" s="9"/>
-      <c r="X12" s="9"/>
-      <c r="Y12" s="10"/>
+      <c r="R12" s="7"/>
+      <c r="S12" s="7"/>
+      <c r="T12" s="7"/>
+      <c r="U12" s="7"/>
+      <c r="V12" s="7"/>
+      <c r="W12" s="7"/>
+      <c r="X12" s="7"/>
+      <c r="Y12" s="8"/>
     </row>
     <row r="13" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B13" s="1"/>
@@ -904,33 +922,33 @@
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="3"/>
-      <c r="G13" s="14">
+      <c r="G13" s="4">
         <v>403</v>
       </c>
-      <c r="H13" s="15"/>
-      <c r="I13" s="14" t="s">
+      <c r="H13" s="5"/>
+      <c r="I13" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="J13" s="15"/>
-      <c r="K13" s="8" t="s">
+      <c r="J13" s="5"/>
+      <c r="K13" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="10"/>
-      <c r="Q13" s="8" t="s">
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="8"/>
+      <c r="Q13" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="R13" s="9"/>
-      <c r="S13" s="9"/>
-      <c r="T13" s="9"/>
-      <c r="U13" s="9"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="10"/>
+      <c r="R13" s="7"/>
+      <c r="S13" s="7"/>
+      <c r="T13" s="7"/>
+      <c r="U13" s="7"/>
+      <c r="V13" s="7"/>
+      <c r="W13" s="7"/>
+      <c r="X13" s="7"/>
+      <c r="Y13" s="8"/>
     </row>
     <row r="14" spans="2:25" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="1"/>
@@ -938,31 +956,31 @@
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="3"/>
-      <c r="G14" s="14">
+      <c r="G14" s="4">
         <v>400</v>
       </c>
-      <c r="H14" s="15"/>
-      <c r="I14" s="14" t="s">
+      <c r="H14" s="5"/>
+      <c r="I14" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="J14" s="15"/>
-      <c r="K14" s="11" t="s">
+      <c r="J14" s="5"/>
+      <c r="K14" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="L14" s="12"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="12"/>
-      <c r="O14" s="12"/>
-      <c r="P14" s="13"/>
-      <c r="Q14" s="8"/>
-      <c r="R14" s="9"/>
-      <c r="S14" s="9"/>
-      <c r="T14" s="9"/>
-      <c r="U14" s="9"/>
-      <c r="V14" s="9"/>
-      <c r="W14" s="9"/>
-      <c r="X14" s="9"/>
-      <c r="Y14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="6"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="7"/>
+      <c r="V14" s="7"/>
+      <c r="W14" s="7"/>
+      <c r="X14" s="7"/>
+      <c r="Y14" s="8"/>
     </row>
     <row r="15" spans="2:25" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="1"/>
@@ -970,31 +988,31 @@
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="3"/>
-      <c r="G15" s="14">
+      <c r="G15" s="4">
         <v>400</v>
       </c>
-      <c r="H15" s="15"/>
-      <c r="I15" s="14" t="s">
+      <c r="H15" s="5"/>
+      <c r="I15" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="J15" s="15"/>
-      <c r="K15" s="11" t="s">
+      <c r="J15" s="5"/>
+      <c r="K15" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="L15" s="12"/>
-      <c r="M15" s="12"/>
-      <c r="N15" s="12"/>
-      <c r="O15" s="12"/>
-      <c r="P15" s="13"/>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="9"/>
-      <c r="S15" s="9"/>
-      <c r="T15" s="9"/>
-      <c r="U15" s="9"/>
-      <c r="V15" s="9"/>
-      <c r="W15" s="9"/>
-      <c r="X15" s="9"/>
-      <c r="Y15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="6"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="7"/>
+      <c r="U15" s="7"/>
+      <c r="V15" s="7"/>
+      <c r="W15" s="7"/>
+      <c r="X15" s="7"/>
+      <c r="Y15" s="8"/>
     </row>
     <row r="16" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B16" s="1"/>
@@ -1002,25 +1020,25 @@
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="3"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
-      <c r="P16" s="10"/>
-      <c r="Q16" s="8"/>
-      <c r="R16" s="9"/>
-      <c r="S16" s="9"/>
-      <c r="T16" s="9"/>
-      <c r="U16" s="9"/>
-      <c r="V16" s="9"/>
-      <c r="W16" s="9"/>
-      <c r="X16" s="9"/>
-      <c r="Y16" s="10"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="8"/>
+      <c r="Q16" s="6"/>
+      <c r="R16" s="7"/>
+      <c r="S16" s="7"/>
+      <c r="T16" s="7"/>
+      <c r="U16" s="7"/>
+      <c r="V16" s="7"/>
+      <c r="W16" s="7"/>
+      <c r="X16" s="7"/>
+      <c r="Y16" s="8"/>
     </row>
     <row r="17" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B17" s="1"/>
@@ -1028,25 +1046,25 @@
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="3"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
-      <c r="P17" s="10"/>
-      <c r="Q17" s="8"/>
-      <c r="R17" s="9"/>
-      <c r="S17" s="9"/>
-      <c r="T17" s="9"/>
-      <c r="U17" s="9"/>
-      <c r="V17" s="9"/>
-      <c r="W17" s="9"/>
-      <c r="X17" s="9"/>
-      <c r="Y17" s="10"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="8"/>
+      <c r="Q17" s="6"/>
+      <c r="R17" s="7"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7"/>
+      <c r="U17" s="7"/>
+      <c r="V17" s="7"/>
+      <c r="W17" s="7"/>
+      <c r="X17" s="7"/>
+      <c r="Y17" s="8"/>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B18" s="1"/>
@@ -1054,33 +1072,33 @@
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="3"/>
-      <c r="G18" s="14">
+      <c r="G18" s="4">
         <v>400</v>
       </c>
-      <c r="H18" s="15"/>
-      <c r="I18" s="14" t="s">
+      <c r="H18" s="5"/>
+      <c r="I18" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="J18" s="15"/>
-      <c r="K18" s="8" t="s">
+      <c r="J18" s="5"/>
+      <c r="K18" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
-      <c r="P18" s="10"/>
-      <c r="Q18" s="8" t="s">
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="8"/>
+      <c r="Q18" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="R18" s="9"/>
-      <c r="S18" s="9"/>
-      <c r="T18" s="9"/>
-      <c r="U18" s="9"/>
-      <c r="V18" s="9"/>
-      <c r="W18" s="9"/>
-      <c r="X18" s="9"/>
-      <c r="Y18" s="10"/>
+      <c r="R18" s="7"/>
+      <c r="S18" s="7"/>
+      <c r="T18" s="7"/>
+      <c r="U18" s="7"/>
+      <c r="V18" s="7"/>
+      <c r="W18" s="7"/>
+      <c r="X18" s="7"/>
+      <c r="Y18" s="8"/>
     </row>
     <row r="19" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B19" s="1"/>
@@ -1088,31 +1106,31 @@
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="3"/>
-      <c r="G19" s="14">
+      <c r="G19" s="4">
         <v>400</v>
       </c>
-      <c r="H19" s="15"/>
-      <c r="I19" s="14" t="s">
+      <c r="H19" s="5"/>
+      <c r="I19" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="J19" s="15"/>
-      <c r="K19" s="8" t="s">
+      <c r="J19" s="5"/>
+      <c r="K19" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="9"/>
-      <c r="P19" s="10"/>
-      <c r="Q19" s="8"/>
-      <c r="R19" s="9"/>
-      <c r="S19" s="9"/>
-      <c r="T19" s="9"/>
-      <c r="U19" s="9"/>
-      <c r="V19" s="9"/>
-      <c r="W19" s="9"/>
-      <c r="X19" s="9"/>
-      <c r="Y19" s="10"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
+      <c r="O19" s="7"/>
+      <c r="P19" s="8"/>
+      <c r="Q19" s="6"/>
+      <c r="R19" s="7"/>
+      <c r="S19" s="7"/>
+      <c r="T19" s="7"/>
+      <c r="U19" s="7"/>
+      <c r="V19" s="7"/>
+      <c r="W19" s="7"/>
+      <c r="X19" s="7"/>
+      <c r="Y19" s="8"/>
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B20" s="1"/>
@@ -1120,25 +1138,25 @@
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
       <c r="F20" s="3"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
-      <c r="P20" s="10"/>
-      <c r="Q20" s="8"/>
-      <c r="R20" s="9"/>
-      <c r="S20" s="9"/>
-      <c r="T20" s="9"/>
-      <c r="U20" s="9"/>
-      <c r="V20" s="9"/>
-      <c r="W20" s="9"/>
-      <c r="X20" s="9"/>
-      <c r="Y20" s="10"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
+      <c r="O20" s="7"/>
+      <c r="P20" s="8"/>
+      <c r="Q20" s="6"/>
+      <c r="R20" s="7"/>
+      <c r="S20" s="7"/>
+      <c r="T20" s="7"/>
+      <c r="U20" s="7"/>
+      <c r="V20" s="7"/>
+      <c r="W20" s="7"/>
+      <c r="X20" s="7"/>
+      <c r="Y20" s="8"/>
     </row>
     <row r="21" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
@@ -1148,33 +1166,33 @@
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="3"/>
-      <c r="G21" s="14">
+      <c r="G21" s="4">
         <v>400</v>
       </c>
-      <c r="H21" s="15"/>
-      <c r="I21" s="14" t="s">
+      <c r="H21" s="5"/>
+      <c r="I21" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="J21" s="15"/>
-      <c r="K21" s="8" t="s">
+      <c r="J21" s="5"/>
+      <c r="K21" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="9"/>
-      <c r="O21" s="9"/>
-      <c r="P21" s="10"/>
-      <c r="Q21" s="8" t="s">
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="7"/>
+      <c r="O21" s="7"/>
+      <c r="P21" s="8"/>
+      <c r="Q21" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="R21" s="9"/>
-      <c r="S21" s="9"/>
-      <c r="T21" s="9"/>
-      <c r="U21" s="9"/>
-      <c r="V21" s="9"/>
-      <c r="W21" s="9"/>
-      <c r="X21" s="9"/>
-      <c r="Y21" s="10"/>
+      <c r="R21" s="7"/>
+      <c r="S21" s="7"/>
+      <c r="T21" s="7"/>
+      <c r="U21" s="7"/>
+      <c r="V21" s="7"/>
+      <c r="W21" s="7"/>
+      <c r="X21" s="7"/>
+      <c r="Y21" s="8"/>
     </row>
     <row r="22" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
@@ -1184,59 +1202,69 @@
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="3"/>
-      <c r="G22" s="14">
+      <c r="G22" s="4">
         <v>403</v>
       </c>
-      <c r="H22" s="15"/>
-      <c r="I22" s="14" t="s">
+      <c r="H22" s="5"/>
+      <c r="I22" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J22" s="15"/>
-      <c r="K22" s="8" t="s">
+      <c r="J22" s="5"/>
+      <c r="K22" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
-      <c r="P22" s="10"/>
-      <c r="Q22" s="8" t="s">
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="7"/>
+      <c r="O22" s="7"/>
+      <c r="P22" s="8"/>
+      <c r="Q22" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="R22" s="9"/>
-      <c r="S22" s="9"/>
-      <c r="T22" s="9"/>
-      <c r="U22" s="9"/>
-      <c r="V22" s="9"/>
-      <c r="W22" s="9"/>
-      <c r="X22" s="9"/>
-      <c r="Y22" s="10"/>
+      <c r="R22" s="7"/>
+      <c r="S22" s="7"/>
+      <c r="T22" s="7"/>
+      <c r="U22" s="7"/>
+      <c r="V22" s="7"/>
+      <c r="W22" s="7"/>
+      <c r="X22" s="7"/>
+      <c r="Y22" s="8"/>
     </row>
     <row r="23" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B23" s="1"/>
+      <c r="B23" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
       <c r="F23" s="3"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="15"/>
-      <c r="K23" s="8"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="9"/>
-      <c r="N23" s="9"/>
-      <c r="O23" s="9"/>
-      <c r="P23" s="10"/>
-      <c r="Q23" s="8"/>
-      <c r="R23" s="9"/>
-      <c r="S23" s="9"/>
-      <c r="T23" s="9"/>
-      <c r="U23" s="9"/>
-      <c r="V23" s="9"/>
-      <c r="W23" s="9"/>
-      <c r="X23" s="9"/>
-      <c r="Y23" s="10"/>
+      <c r="G23" s="4">
+        <v>400</v>
+      </c>
+      <c r="H23" s="5"/>
+      <c r="I23" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J23" s="5"/>
+      <c r="K23" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7"/>
+      <c r="O23" s="7"/>
+      <c r="P23" s="8"/>
+      <c r="Q23" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="R23" s="7"/>
+      <c r="S23" s="7"/>
+      <c r="T23" s="7"/>
+      <c r="U23" s="7"/>
+      <c r="V23" s="7"/>
+      <c r="W23" s="7"/>
+      <c r="X23" s="7"/>
+      <c r="Y23" s="8"/>
     </row>
     <row r="24" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B24" s="1"/>
@@ -1244,25 +1272,25 @@
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
       <c r="F24" s="3"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="15"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="9"/>
-      <c r="N24" s="9"/>
-      <c r="O24" s="9"/>
-      <c r="P24" s="10"/>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="9"/>
-      <c r="S24" s="9"/>
-      <c r="T24" s="9"/>
-      <c r="U24" s="9"/>
-      <c r="V24" s="9"/>
-      <c r="W24" s="9"/>
-      <c r="X24" s="9"/>
-      <c r="Y24" s="10"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="7"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="7"/>
+      <c r="O24" s="7"/>
+      <c r="P24" s="8"/>
+      <c r="Q24" s="6"/>
+      <c r="R24" s="7"/>
+      <c r="S24" s="7"/>
+      <c r="T24" s="7"/>
+      <c r="U24" s="7"/>
+      <c r="V24" s="7"/>
+      <c r="W24" s="7"/>
+      <c r="X24" s="7"/>
+      <c r="Y24" s="8"/>
     </row>
     <row r="25" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B25" s="1"/>
@@ -1270,25 +1298,25 @@
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
       <c r="F25" s="3"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="15"/>
-      <c r="K25" s="8"/>
-      <c r="L25" s="9"/>
-      <c r="M25" s="9"/>
-      <c r="N25" s="9"/>
-      <c r="O25" s="9"/>
-      <c r="P25" s="10"/>
-      <c r="Q25" s="8"/>
-      <c r="R25" s="9"/>
-      <c r="S25" s="9"/>
-      <c r="T25" s="9"/>
-      <c r="U25" s="9"/>
-      <c r="V25" s="9"/>
-      <c r="W25" s="9"/>
-      <c r="X25" s="9"/>
-      <c r="Y25" s="10"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="7"/>
+      <c r="O25" s="7"/>
+      <c r="P25" s="8"/>
+      <c r="Q25" s="6"/>
+      <c r="R25" s="7"/>
+      <c r="S25" s="7"/>
+      <c r="T25" s="7"/>
+      <c r="U25" s="7"/>
+      <c r="V25" s="7"/>
+      <c r="W25" s="7"/>
+      <c r="X25" s="7"/>
+      <c r="Y25" s="8"/>
     </row>
     <row r="26" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B26" s="1"/>
@@ -1296,25 +1324,25 @@
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
       <c r="F26" s="3"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="9"/>
-      <c r="M26" s="9"/>
-      <c r="N26" s="9"/>
-      <c r="O26" s="9"/>
-      <c r="P26" s="10"/>
-      <c r="Q26" s="8"/>
-      <c r="R26" s="9"/>
-      <c r="S26" s="9"/>
-      <c r="T26" s="9"/>
-      <c r="U26" s="9"/>
-      <c r="V26" s="9"/>
-      <c r="W26" s="9"/>
-      <c r="X26" s="9"/>
-      <c r="Y26" s="10"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="7"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="7"/>
+      <c r="O26" s="7"/>
+      <c r="P26" s="8"/>
+      <c r="Q26" s="6"/>
+      <c r="R26" s="7"/>
+      <c r="S26" s="7"/>
+      <c r="T26" s="7"/>
+      <c r="U26" s="7"/>
+      <c r="V26" s="7"/>
+      <c r="W26" s="7"/>
+      <c r="X26" s="7"/>
+      <c r="Y26" s="8"/>
     </row>
     <row r="27" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B27" s="1"/>
@@ -1322,25 +1350,25 @@
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
       <c r="F27" s="3"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="8"/>
-      <c r="L27" s="9"/>
-      <c r="M27" s="9"/>
-      <c r="N27" s="9"/>
-      <c r="O27" s="9"/>
-      <c r="P27" s="10"/>
-      <c r="Q27" s="8"/>
-      <c r="R27" s="9"/>
-      <c r="S27" s="9"/>
-      <c r="T27" s="9"/>
-      <c r="U27" s="9"/>
-      <c r="V27" s="9"/>
-      <c r="W27" s="9"/>
-      <c r="X27" s="9"/>
-      <c r="Y27" s="10"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="7"/>
+      <c r="M27" s="7"/>
+      <c r="N27" s="7"/>
+      <c r="O27" s="7"/>
+      <c r="P27" s="8"/>
+      <c r="Q27" s="6"/>
+      <c r="R27" s="7"/>
+      <c r="S27" s="7"/>
+      <c r="T27" s="7"/>
+      <c r="U27" s="7"/>
+      <c r="V27" s="7"/>
+      <c r="W27" s="7"/>
+      <c r="X27" s="7"/>
+      <c r="Y27" s="8"/>
     </row>
     <row r="28" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
@@ -1350,33 +1378,33 @@
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
       <c r="F28" s="3"/>
-      <c r="G28" s="14">
+      <c r="G28" s="4">
         <v>400</v>
       </c>
-      <c r="H28" s="15"/>
-      <c r="I28" s="14" t="s">
+      <c r="H28" s="5"/>
+      <c r="I28" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="J28" s="15"/>
-      <c r="K28" s="8" t="s">
+      <c r="J28" s="5"/>
+      <c r="K28" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="L28" s="9"/>
-      <c r="M28" s="9"/>
-      <c r="N28" s="9"/>
-      <c r="O28" s="9"/>
-      <c r="P28" s="10"/>
-      <c r="Q28" s="8" t="s">
+      <c r="L28" s="7"/>
+      <c r="M28" s="7"/>
+      <c r="N28" s="7"/>
+      <c r="O28" s="7"/>
+      <c r="P28" s="8"/>
+      <c r="Q28" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="R28" s="9"/>
-      <c r="S28" s="9"/>
-      <c r="T28" s="9"/>
-      <c r="U28" s="9"/>
-      <c r="V28" s="9"/>
-      <c r="W28" s="9"/>
-      <c r="X28" s="9"/>
-      <c r="Y28" s="10"/>
+      <c r="R28" s="7"/>
+      <c r="S28" s="7"/>
+      <c r="T28" s="7"/>
+      <c r="U28" s="7"/>
+      <c r="V28" s="7"/>
+      <c r="W28" s="7"/>
+      <c r="X28" s="7"/>
+      <c r="Y28" s="8"/>
     </row>
     <row r="29" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
@@ -1386,59 +1414,69 @@
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
       <c r="F29" s="3"/>
-      <c r="G29" s="14">
+      <c r="G29" s="4">
         <v>400</v>
       </c>
-      <c r="H29" s="15"/>
-      <c r="I29" s="14" t="s">
+      <c r="H29" s="5"/>
+      <c r="I29" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="J29" s="15"/>
-      <c r="K29" s="8" t="s">
+      <c r="J29" s="5"/>
+      <c r="K29" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="L29" s="9"/>
-      <c r="M29" s="9"/>
-      <c r="N29" s="9"/>
-      <c r="O29" s="9"/>
-      <c r="P29" s="10"/>
-      <c r="Q29" s="8" t="s">
+      <c r="L29" s="7"/>
+      <c r="M29" s="7"/>
+      <c r="N29" s="7"/>
+      <c r="O29" s="7"/>
+      <c r="P29" s="8"/>
+      <c r="Q29" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="R29" s="9"/>
-      <c r="S29" s="9"/>
-      <c r="T29" s="9"/>
-      <c r="U29" s="9"/>
-      <c r="V29" s="9"/>
-      <c r="W29" s="9"/>
-      <c r="X29" s="9"/>
-      <c r="Y29" s="10"/>
+      <c r="R29" s="7"/>
+      <c r="S29" s="7"/>
+      <c r="T29" s="7"/>
+      <c r="U29" s="7"/>
+      <c r="V29" s="7"/>
+      <c r="W29" s="7"/>
+      <c r="X29" s="7"/>
+      <c r="Y29" s="8"/>
     </row>
     <row r="30" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B30" s="1"/>
+      <c r="B30" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
       <c r="F30" s="3"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="9"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="9"/>
-      <c r="O30" s="9"/>
-      <c r="P30" s="10"/>
-      <c r="Q30" s="8"/>
-      <c r="R30" s="9"/>
-      <c r="S30" s="9"/>
-      <c r="T30" s="9"/>
-      <c r="U30" s="9"/>
-      <c r="V30" s="9"/>
-      <c r="W30" s="9"/>
-      <c r="X30" s="9"/>
-      <c r="Y30" s="10"/>
+      <c r="G30" s="4">
+        <v>400</v>
+      </c>
+      <c r="H30" s="5"/>
+      <c r="I30" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J30" s="5"/>
+      <c r="K30" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="L30" s="7"/>
+      <c r="M30" s="7"/>
+      <c r="N30" s="7"/>
+      <c r="O30" s="7"/>
+      <c r="P30" s="8"/>
+      <c r="Q30" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="R30" s="7"/>
+      <c r="S30" s="7"/>
+      <c r="T30" s="7"/>
+      <c r="U30" s="7"/>
+      <c r="V30" s="7"/>
+      <c r="W30" s="7"/>
+      <c r="X30" s="7"/>
+      <c r="Y30" s="8"/>
     </row>
     <row r="31" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B31" s="1"/>
@@ -1446,25 +1484,25 @@
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
       <c r="F31" s="3"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="15"/>
-      <c r="K31" s="8"/>
-      <c r="L31" s="9"/>
-      <c r="M31" s="9"/>
-      <c r="N31" s="9"/>
-      <c r="O31" s="9"/>
-      <c r="P31" s="10"/>
-      <c r="Q31" s="8"/>
-      <c r="R31" s="9"/>
-      <c r="S31" s="9"/>
-      <c r="T31" s="9"/>
-      <c r="U31" s="9"/>
-      <c r="V31" s="9"/>
-      <c r="W31" s="9"/>
-      <c r="X31" s="9"/>
-      <c r="Y31" s="10"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="7"/>
+      <c r="M31" s="7"/>
+      <c r="N31" s="7"/>
+      <c r="O31" s="7"/>
+      <c r="P31" s="8"/>
+      <c r="Q31" s="6"/>
+      <c r="R31" s="7"/>
+      <c r="S31" s="7"/>
+      <c r="T31" s="7"/>
+      <c r="U31" s="7"/>
+      <c r="V31" s="7"/>
+      <c r="W31" s="7"/>
+      <c r="X31" s="7"/>
+      <c r="Y31" s="8"/>
     </row>
     <row r="32" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B32" s="1"/>
@@ -1472,25 +1510,25 @@
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
       <c r="F32" s="3"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="14"/>
-      <c r="J32" s="15"/>
-      <c r="K32" s="8"/>
-      <c r="L32" s="9"/>
-      <c r="M32" s="9"/>
-      <c r="N32" s="9"/>
-      <c r="O32" s="9"/>
-      <c r="P32" s="10"/>
-      <c r="Q32" s="8"/>
-      <c r="R32" s="9"/>
-      <c r="S32" s="9"/>
-      <c r="T32" s="9"/>
-      <c r="U32" s="9"/>
-      <c r="V32" s="9"/>
-      <c r="W32" s="9"/>
-      <c r="X32" s="9"/>
-      <c r="Y32" s="10"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="7"/>
+      <c r="M32" s="7"/>
+      <c r="N32" s="7"/>
+      <c r="O32" s="7"/>
+      <c r="P32" s="8"/>
+      <c r="Q32" s="6"/>
+      <c r="R32" s="7"/>
+      <c r="S32" s="7"/>
+      <c r="T32" s="7"/>
+      <c r="U32" s="7"/>
+      <c r="V32" s="7"/>
+      <c r="W32" s="7"/>
+      <c r="X32" s="7"/>
+      <c r="Y32" s="8"/>
     </row>
     <row r="33" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B33" s="1"/>
@@ -1498,25 +1536,25 @@
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
       <c r="F33" s="3"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="14"/>
-      <c r="J33" s="15"/>
-      <c r="K33" s="8"/>
-      <c r="L33" s="9"/>
-      <c r="M33" s="9"/>
-      <c r="N33" s="9"/>
-      <c r="O33" s="9"/>
-      <c r="P33" s="10"/>
-      <c r="Q33" s="8"/>
-      <c r="R33" s="9"/>
-      <c r="S33" s="9"/>
-      <c r="T33" s="9"/>
-      <c r="U33" s="9"/>
-      <c r="V33" s="9"/>
-      <c r="W33" s="9"/>
-      <c r="X33" s="9"/>
-      <c r="Y33" s="10"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="7"/>
+      <c r="M33" s="7"/>
+      <c r="N33" s="7"/>
+      <c r="O33" s="7"/>
+      <c r="P33" s="8"/>
+      <c r="Q33" s="6"/>
+      <c r="R33" s="7"/>
+      <c r="S33" s="7"/>
+      <c r="T33" s="7"/>
+      <c r="U33" s="7"/>
+      <c r="V33" s="7"/>
+      <c r="W33" s="7"/>
+      <c r="X33" s="7"/>
+      <c r="Y33" s="8"/>
     </row>
     <row r="34" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B34" s="1"/>
@@ -1524,25 +1562,25 @@
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
       <c r="F34" s="3"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="14"/>
-      <c r="J34" s="15"/>
-      <c r="K34" s="8"/>
-      <c r="L34" s="9"/>
-      <c r="M34" s="9"/>
-      <c r="N34" s="9"/>
-      <c r="O34" s="9"/>
-      <c r="P34" s="10"/>
-      <c r="Q34" s="8"/>
-      <c r="R34" s="9"/>
-      <c r="S34" s="9"/>
-      <c r="T34" s="9"/>
-      <c r="U34" s="9"/>
-      <c r="V34" s="9"/>
-      <c r="W34" s="9"/>
-      <c r="X34" s="9"/>
-      <c r="Y34" s="10"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="7"/>
+      <c r="M34" s="7"/>
+      <c r="N34" s="7"/>
+      <c r="O34" s="7"/>
+      <c r="P34" s="8"/>
+      <c r="Q34" s="6"/>
+      <c r="R34" s="7"/>
+      <c r="S34" s="7"/>
+      <c r="T34" s="7"/>
+      <c r="U34" s="7"/>
+      <c r="V34" s="7"/>
+      <c r="W34" s="7"/>
+      <c r="X34" s="7"/>
+      <c r="Y34" s="8"/>
     </row>
     <row r="35" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B35" s="1"/>
@@ -1550,92 +1588,91 @@
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
       <c r="F35" s="3"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="15"/>
-      <c r="I35" s="14"/>
-      <c r="J35" s="15"/>
-      <c r="K35" s="8"/>
-      <c r="L35" s="9"/>
-      <c r="M35" s="9"/>
-      <c r="N35" s="9"/>
-      <c r="O35" s="9"/>
-      <c r="P35" s="10"/>
-      <c r="Q35" s="8"/>
-      <c r="R35" s="9"/>
-      <c r="S35" s="9"/>
-      <c r="T35" s="9"/>
-      <c r="U35" s="9"/>
-      <c r="V35" s="9"/>
-      <c r="W35" s="9"/>
-      <c r="X35" s="9"/>
-      <c r="Y35" s="10"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="7"/>
+      <c r="M35" s="7"/>
+      <c r="N35" s="7"/>
+      <c r="O35" s="7"/>
+      <c r="P35" s="8"/>
+      <c r="Q35" s="6"/>
+      <c r="R35" s="7"/>
+      <c r="S35" s="7"/>
+      <c r="T35" s="7"/>
+      <c r="U35" s="7"/>
+      <c r="V35" s="7"/>
+      <c r="W35" s="7"/>
+      <c r="X35" s="7"/>
+      <c r="Y35" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="151">
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="K22:P22"/>
-    <mergeCell ref="Q22:Y22"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="K23:P23"/>
-    <mergeCell ref="Q23:Y23"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K20:P20"/>
-    <mergeCell ref="Q20:Y20"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K21:P21"/>
-    <mergeCell ref="Q21:Y21"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="K26:P26"/>
-    <mergeCell ref="Q26:Y26"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="K24:P24"/>
-    <mergeCell ref="Q24:Y24"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="K25:P25"/>
-    <mergeCell ref="Q25:Y25"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="K15:P15"/>
-    <mergeCell ref="Q15:Y15"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="K19:P19"/>
-    <mergeCell ref="Q19:Y19"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="K16:P16"/>
-    <mergeCell ref="Q16:Y16"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:P8"/>
-    <mergeCell ref="Q8:Y8"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K6:P6"/>
-    <mergeCell ref="Q6:Y6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:P7"/>
-    <mergeCell ref="Q7:Y7"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B2:Y4"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="K35:P35"/>
+    <mergeCell ref="Q35:Y35"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="K33:P33"/>
+    <mergeCell ref="Q33:Y33"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="K34:P34"/>
+    <mergeCell ref="Q34:Y34"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="K31:P31"/>
+    <mergeCell ref="Q31:Y31"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="K32:P32"/>
+    <mergeCell ref="Q32:Y32"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="K29:P29"/>
+    <mergeCell ref="Q29:Y29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="K30:P30"/>
+    <mergeCell ref="Q30:Y30"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="Q13:Y13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="K14:P14"/>
+    <mergeCell ref="Q14:Y14"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:P17"/>
+    <mergeCell ref="Q17:Y17"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:P12"/>
+    <mergeCell ref="Q12:Y12"/>
+    <mergeCell ref="I13:J13"/>
     <mergeCell ref="G28:H28"/>
     <mergeCell ref="G18:H18"/>
     <mergeCell ref="I18:J18"/>
@@ -1660,69 +1697,70 @@
     <mergeCell ref="K28:P28"/>
     <mergeCell ref="Q28:Y28"/>
     <mergeCell ref="K13:P13"/>
-    <mergeCell ref="Q13:Y13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="K14:P14"/>
-    <mergeCell ref="Q14:Y14"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:P17"/>
-    <mergeCell ref="Q17:Y17"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:P12"/>
-    <mergeCell ref="Q12:Y12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="K31:P31"/>
-    <mergeCell ref="Q31:Y31"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="K32:P32"/>
-    <mergeCell ref="Q32:Y32"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="K29:P29"/>
-    <mergeCell ref="Q29:Y29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="K30:P30"/>
-    <mergeCell ref="Q30:Y30"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="K35:P35"/>
-    <mergeCell ref="Q35:Y35"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="K33:P33"/>
-    <mergeCell ref="Q33:Y33"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="K34:P34"/>
-    <mergeCell ref="Q34:Y34"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="B2:Y4"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:P8"/>
+    <mergeCell ref="Q8:Y8"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K6:P6"/>
+    <mergeCell ref="Q6:Y6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:P7"/>
+    <mergeCell ref="Q7:Y7"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="K15:P15"/>
+    <mergeCell ref="Q15:Y15"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="K19:P19"/>
+    <mergeCell ref="Q19:Y19"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="K16:P16"/>
+    <mergeCell ref="Q16:Y16"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="K26:P26"/>
+    <mergeCell ref="Q26:Y26"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="K24:P24"/>
+    <mergeCell ref="Q24:Y24"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="K25:P25"/>
+    <mergeCell ref="Q25:Y25"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K20:P20"/>
+    <mergeCell ref="Q20:Y20"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:P21"/>
+    <mergeCell ref="Q21:Y21"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="K22:P22"/>
+    <mergeCell ref="Q22:Y22"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="K23:P23"/>
+    <mergeCell ref="Q23:Y23"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/documentAPI.xlsx
+++ b/documentAPI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my-project\shop-backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0251636-FA5E-4B36-926F-9C1D56FED9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EB7A0A9-2FBA-4A4E-8028-82B193657BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="63">
   <si>
     <t>Error Code</t>
   </si>
@@ -175,6 +175,45 @@
   </si>
   <si>
     <t>Error when update verification code in database</t>
+  </si>
+  <si>
+    <t>E4003</t>
+  </si>
+  <si>
+    <t>The verification code is required!</t>
+  </si>
+  <si>
+    <t>The user already authenticated!</t>
+  </si>
+  <si>
+    <t>The user information not found!</t>
+  </si>
+  <si>
+    <t>The user does not exist in database!</t>
+  </si>
+  <si>
+    <t>E4004</t>
+  </si>
+  <si>
+    <t>E4005</t>
+  </si>
+  <si>
+    <t>No authentication information found!</t>
+  </si>
+  <si>
+    <t>The verification code has expired!</t>
+  </si>
+  <si>
+    <t>The verification code is incorrect!</t>
+  </si>
+  <si>
+    <t>E8003</t>
+  </si>
+  <si>
+    <t>Error when user verification!</t>
+  </si>
+  <si>
+    <t>Error when update user of the verification in database</t>
   </si>
 </sst>
 </file>
@@ -270,6 +309,15 @@
   <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -283,15 +331,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
@@ -594,7 +633,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:Y35"/>
+  <dimension ref="B2:Y38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="16" max="16" width="9.140625" customWidth="1"/>
@@ -717,253 +756,253 @@
       <c r="Y6" s="13"/>
     </row>
     <row r="7" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="4" t="s">
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="5"/>
-      <c r="K7" s="6" t="s">
+      <c r="J7" s="8"/>
+      <c r="K7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="7"/>
-      <c r="S7" s="7"/>
-      <c r="T7" s="7"/>
-      <c r="U7" s="7"/>
-      <c r="V7" s="7"/>
-      <c r="W7" s="7"/>
-      <c r="X7" s="7"/>
-      <c r="Y7" s="8"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2"/>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
+      <c r="Y7" s="3"/>
     </row>
     <row r="8" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B8" s="1"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="4">
+      <c r="B8" s="4"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="7">
         <v>400</v>
       </c>
-      <c r="H8" s="5"/>
-      <c r="I8" s="4" t="s">
+      <c r="H8" s="8"/>
+      <c r="I8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="J8" s="5"/>
-      <c r="K8" s="6" t="s">
+      <c r="J8" s="8"/>
+      <c r="K8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="7"/>
-      <c r="S8" s="7"/>
-      <c r="T8" s="7"/>
-      <c r="U8" s="7"/>
-      <c r="V8" s="7"/>
-      <c r="W8" s="7"/>
-      <c r="X8" s="7"/>
-      <c r="Y8" s="8"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="2"/>
+      <c r="W8" s="2"/>
+      <c r="X8" s="2"/>
+      <c r="Y8" s="3"/>
     </row>
     <row r="9" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B9" s="1"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="4">
+      <c r="B9" s="4"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="7">
         <v>401</v>
       </c>
-      <c r="H9" s="5"/>
-      <c r="I9" s="4" t="s">
+      <c r="H9" s="8"/>
+      <c r="I9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="J9" s="5"/>
-      <c r="K9" s="6" t="s">
+      <c r="J9" s="8"/>
+      <c r="K9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="6" t="s">
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R9" s="7"/>
-      <c r="S9" s="7"/>
-      <c r="T9" s="7"/>
-      <c r="U9" s="7"/>
-      <c r="V9" s="7"/>
-      <c r="W9" s="7"/>
-      <c r="X9" s="7"/>
-      <c r="Y9" s="8"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
+      <c r="W9" s="2"/>
+      <c r="X9" s="2"/>
+      <c r="Y9" s="3"/>
     </row>
     <row r="10" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B10" s="1"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="4">
+      <c r="B10" s="4"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="7">
         <v>400</v>
       </c>
-      <c r="H10" s="5"/>
-      <c r="I10" s="4" t="s">
+      <c r="H10" s="8"/>
+      <c r="I10" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="J10" s="5"/>
-      <c r="K10" s="6" t="s">
+      <c r="J10" s="8"/>
+      <c r="K10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
-      <c r="P10" s="8"/>
-      <c r="Q10" s="6" t="s">
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="R10" s="7"/>
-      <c r="S10" s="7"/>
-      <c r="T10" s="7"/>
-      <c r="U10" s="7"/>
-      <c r="V10" s="7"/>
-      <c r="W10" s="7"/>
-      <c r="X10" s="7"/>
-      <c r="Y10" s="8"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2"/>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
+      <c r="Y10" s="3"/>
     </row>
     <row r="11" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B11" s="1"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="4">
+      <c r="B11" s="4"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="7">
         <v>400</v>
       </c>
-      <c r="H11" s="5"/>
-      <c r="I11" s="4" t="s">
+      <c r="H11" s="8"/>
+      <c r="I11" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="J11" s="5"/>
-      <c r="K11" s="6" t="s">
+      <c r="J11" s="8"/>
+      <c r="K11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
-      <c r="P11" s="8"/>
-      <c r="Q11" s="6" t="s">
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="R11" s="7"/>
-      <c r="S11" s="7"/>
-      <c r="T11" s="7"/>
-      <c r="U11" s="7"/>
-      <c r="V11" s="7"/>
-      <c r="W11" s="7"/>
-      <c r="X11" s="7"/>
-      <c r="Y11" s="8"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
+      <c r="T11" s="2"/>
+      <c r="U11" s="2"/>
+      <c r="V11" s="2"/>
+      <c r="W11" s="2"/>
+      <c r="X11" s="2"/>
+      <c r="Y11" s="3"/>
     </row>
     <row r="12" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B12" s="1"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="4">
+      <c r="B12" s="4"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="7">
         <v>400</v>
       </c>
-      <c r="H12" s="5"/>
-      <c r="I12" s="4" t="s">
+      <c r="H12" s="8"/>
+      <c r="I12" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="J12" s="5"/>
-      <c r="K12" s="6" t="s">
+      <c r="J12" s="8"/>
+      <c r="K12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="6" t="s">
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="R12" s="7"/>
-      <c r="S12" s="7"/>
-      <c r="T12" s="7"/>
-      <c r="U12" s="7"/>
-      <c r="V12" s="7"/>
-      <c r="W12" s="7"/>
-      <c r="X12" s="7"/>
-      <c r="Y12" s="8"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
+      <c r="V12" s="2"/>
+      <c r="W12" s="2"/>
+      <c r="X12" s="2"/>
+      <c r="Y12" s="3"/>
     </row>
     <row r="13" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B13" s="1"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="4">
+      <c r="B13" s="4"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="7">
         <v>403</v>
       </c>
-      <c r="H13" s="5"/>
-      <c r="I13" s="4" t="s">
+      <c r="H13" s="8"/>
+      <c r="I13" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="J13" s="5"/>
-      <c r="K13" s="6" t="s">
+      <c r="J13" s="8"/>
+      <c r="K13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="8"/>
-      <c r="Q13" s="6" t="s">
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="R13" s="7"/>
-      <c r="S13" s="7"/>
-      <c r="T13" s="7"/>
-      <c r="U13" s="7"/>
-      <c r="V13" s="7"/>
-      <c r="W13" s="7"/>
-      <c r="X13" s="7"/>
-      <c r="Y13" s="8"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+      <c r="T13" s="2"/>
+      <c r="U13" s="2"/>
+      <c r="V13" s="2"/>
+      <c r="W13" s="2"/>
+      <c r="X13" s="2"/>
+      <c r="Y13" s="3"/>
     </row>
     <row r="14" spans="2:25" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="1"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="4">
+      <c r="B14" s="4"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="7">
         <v>400</v>
       </c>
-      <c r="H14" s="5"/>
-      <c r="I14" s="4" t="s">
+      <c r="H14" s="8"/>
+      <c r="I14" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="J14" s="5"/>
+      <c r="J14" s="8"/>
       <c r="K14" s="9" t="s">
         <v>31</v>
       </c>
@@ -972,30 +1011,30 @@
       <c r="N14" s="10"/>
       <c r="O14" s="10"/>
       <c r="P14" s="11"/>
-      <c r="Q14" s="6"/>
-      <c r="R14" s="7"/>
-      <c r="S14" s="7"/>
-      <c r="T14" s="7"/>
-      <c r="U14" s="7"/>
-      <c r="V14" s="7"/>
-      <c r="W14" s="7"/>
-      <c r="X14" s="7"/>
-      <c r="Y14" s="8"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="2"/>
+      <c r="U14" s="2"/>
+      <c r="V14" s="2"/>
+      <c r="W14" s="2"/>
+      <c r="X14" s="2"/>
+      <c r="Y14" s="3"/>
     </row>
     <row r="15" spans="2:25" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="1"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="4">
+      <c r="B15" s="4"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="7">
         <v>400</v>
       </c>
-      <c r="H15" s="5"/>
-      <c r="I15" s="4" t="s">
+      <c r="H15" s="8"/>
+      <c r="I15" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="J15" s="5"/>
+      <c r="J15" s="8"/>
       <c r="K15" s="9" t="s">
         <v>32</v>
       </c>
@@ -1004,621 +1043,749 @@
       <c r="N15" s="10"/>
       <c r="O15" s="10"/>
       <c r="P15" s="11"/>
-      <c r="Q15" s="6"/>
-      <c r="R15" s="7"/>
-      <c r="S15" s="7"/>
-      <c r="T15" s="7"/>
-      <c r="U15" s="7"/>
-      <c r="V15" s="7"/>
-      <c r="W15" s="7"/>
-      <c r="X15" s="7"/>
-      <c r="Y15" s="8"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
+      <c r="Y15" s="3"/>
     </row>
     <row r="16" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B16" s="1"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="8"/>
-      <c r="Q16" s="6"/>
-      <c r="R16" s="7"/>
-      <c r="S16" s="7"/>
-      <c r="T16" s="7"/>
-      <c r="U16" s="7"/>
-      <c r="V16" s="7"/>
-      <c r="W16" s="7"/>
-      <c r="X16" s="7"/>
-      <c r="Y16" s="8"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+      <c r="V16" s="2"/>
+      <c r="W16" s="2"/>
+      <c r="X16" s="2"/>
+      <c r="Y16" s="3"/>
     </row>
     <row r="17" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B17" s="1"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="7"/>
-      <c r="P17" s="8"/>
-      <c r="Q17" s="6"/>
-      <c r="R17" s="7"/>
-      <c r="S17" s="7"/>
-      <c r="T17" s="7"/>
-      <c r="U17" s="7"/>
-      <c r="V17" s="7"/>
-      <c r="W17" s="7"/>
-      <c r="X17" s="7"/>
-      <c r="Y17" s="8"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="2"/>
+      <c r="W17" s="2"/>
+      <c r="X17" s="2"/>
+      <c r="Y17" s="3"/>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B18" s="1"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="4">
+      <c r="B18" s="4"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="7">
         <v>400</v>
       </c>
-      <c r="H18" s="5"/>
-      <c r="I18" s="4" t="s">
+      <c r="H18" s="8"/>
+      <c r="I18" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="J18" s="5"/>
-      <c r="K18" s="6" t="s">
+      <c r="J18" s="8"/>
+      <c r="K18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="7"/>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="6" t="s">
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="R18" s="7"/>
-      <c r="S18" s="7"/>
-      <c r="T18" s="7"/>
-      <c r="U18" s="7"/>
-      <c r="V18" s="7"/>
-      <c r="W18" s="7"/>
-      <c r="X18" s="7"/>
-      <c r="Y18" s="8"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="2"/>
+      <c r="W18" s="2"/>
+      <c r="X18" s="2"/>
+      <c r="Y18" s="3"/>
     </row>
     <row r="19" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B19" s="1"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="4">
+      <c r="B19" s="4"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="7">
         <v>400</v>
       </c>
-      <c r="H19" s="5"/>
-      <c r="I19" s="4" t="s">
+      <c r="H19" s="8"/>
+      <c r="I19" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="J19" s="5"/>
-      <c r="K19" s="6" t="s">
+      <c r="J19" s="8"/>
+      <c r="K19" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="7"/>
-      <c r="O19" s="7"/>
-      <c r="P19" s="8"/>
-      <c r="Q19" s="6"/>
-      <c r="R19" s="7"/>
-      <c r="S19" s="7"/>
-      <c r="T19" s="7"/>
-      <c r="U19" s="7"/>
-      <c r="V19" s="7"/>
-      <c r="W19" s="7"/>
-      <c r="X19" s="7"/>
-      <c r="Y19" s="8"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2"/>
+      <c r="W19" s="2"/>
+      <c r="X19" s="2"/>
+      <c r="Y19" s="3"/>
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B20" s="1"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
-      <c r="O20" s="7"/>
-      <c r="P20" s="8"/>
-      <c r="Q20" s="6"/>
-      <c r="R20" s="7"/>
-      <c r="S20" s="7"/>
-      <c r="T20" s="7"/>
-      <c r="U20" s="7"/>
-      <c r="V20" s="7"/>
-      <c r="W20" s="7"/>
-      <c r="X20" s="7"/>
-      <c r="Y20" s="8"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2"/>
+      <c r="V20" s="2"/>
+      <c r="W20" s="2"/>
+      <c r="X20" s="2"/>
+      <c r="Y20" s="3"/>
     </row>
     <row r="21" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="4">
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="7">
         <v>400</v>
       </c>
-      <c r="H21" s="5"/>
-      <c r="I21" s="4" t="s">
+      <c r="H21" s="8"/>
+      <c r="I21" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="J21" s="5"/>
-      <c r="K21" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="7"/>
-      <c r="O21" s="7"/>
-      <c r="P21" s="8"/>
-      <c r="Q21" s="6" t="s">
+      <c r="J21" s="8"/>
+      <c r="K21" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="3"/>
+      <c r="Q21" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="R21" s="7"/>
-      <c r="S21" s="7"/>
-      <c r="T21" s="7"/>
-      <c r="U21" s="7"/>
-      <c r="V21" s="7"/>
-      <c r="W21" s="7"/>
-      <c r="X21" s="7"/>
-      <c r="Y21" s="8"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="2"/>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2"/>
+      <c r="V21" s="2"/>
+      <c r="W21" s="2"/>
+      <c r="X21" s="2"/>
+      <c r="Y21" s="3"/>
     </row>
     <row r="22" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="4">
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="7">
         <v>403</v>
       </c>
-      <c r="H22" s="5"/>
-      <c r="I22" s="4" t="s">
+      <c r="H22" s="8"/>
+      <c r="I22" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="J22" s="5"/>
-      <c r="K22" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="7"/>
-      <c r="O22" s="7"/>
-      <c r="P22" s="8"/>
-      <c r="Q22" s="6" t="s">
+      <c r="J22" s="8"/>
+      <c r="K22" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="R22" s="7"/>
-      <c r="S22" s="7"/>
-      <c r="T22" s="7"/>
-      <c r="U22" s="7"/>
-      <c r="V22" s="7"/>
-      <c r="W22" s="7"/>
-      <c r="X22" s="7"/>
-      <c r="Y22" s="8"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="2"/>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2"/>
+      <c r="V22" s="2"/>
+      <c r="W22" s="2"/>
+      <c r="X22" s="2"/>
+      <c r="Y22" s="3"/>
     </row>
     <row r="23" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="4">
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="7">
         <v>400</v>
       </c>
-      <c r="H23" s="5"/>
-      <c r="I23" s="4" t="s">
+      <c r="H23" s="8"/>
+      <c r="I23" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="J23" s="5"/>
-      <c r="K23" s="6" t="s">
+      <c r="J23" s="8"/>
+      <c r="K23" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="7"/>
-      <c r="O23" s="7"/>
-      <c r="P23" s="8"/>
-      <c r="Q23" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="R23" s="7"/>
-      <c r="S23" s="7"/>
-      <c r="T23" s="7"/>
-      <c r="U23" s="7"/>
-      <c r="V23" s="7"/>
-      <c r="W23" s="7"/>
-      <c r="X23" s="7"/>
-      <c r="Y23" s="8"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="2"/>
+      <c r="T23" s="2"/>
+      <c r="U23" s="2"/>
+      <c r="V23" s="2"/>
+      <c r="W23" s="2"/>
+      <c r="X23" s="2"/>
+      <c r="Y23" s="3"/>
     </row>
     <row r="24" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B24" s="1"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="7"/>
-      <c r="O24" s="7"/>
-      <c r="P24" s="8"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="7"/>
-      <c r="S24" s="7"/>
-      <c r="T24" s="7"/>
-      <c r="U24" s="7"/>
-      <c r="V24" s="7"/>
-      <c r="W24" s="7"/>
-      <c r="X24" s="7"/>
-      <c r="Y24" s="8"/>
+      <c r="B24" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="7">
+        <v>400</v>
+      </c>
+      <c r="H24" s="8"/>
+      <c r="I24" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J24" s="8"/>
+      <c r="K24" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="R24" s="2"/>
+      <c r="S24" s="2"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="2"/>
+      <c r="W24" s="2"/>
+      <c r="X24" s="2"/>
+      <c r="Y24" s="3"/>
     </row>
     <row r="25" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B25" s="1"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="5"/>
-      <c r="K25" s="6"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
-      <c r="N25" s="7"/>
-      <c r="O25" s="7"/>
-      <c r="P25" s="8"/>
-      <c r="Q25" s="6"/>
-      <c r="R25" s="7"/>
-      <c r="S25" s="7"/>
-      <c r="T25" s="7"/>
-      <c r="U25" s="7"/>
-      <c r="V25" s="7"/>
-      <c r="W25" s="7"/>
-      <c r="X25" s="7"/>
-      <c r="Y25" s="8"/>
+      <c r="B25" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="7">
+        <v>403</v>
+      </c>
+      <c r="H25" s="8"/>
+      <c r="I25" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="J25" s="8"/>
+      <c r="K25" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R25" s="2"/>
+      <c r="S25" s="2"/>
+      <c r="T25" s="2"/>
+      <c r="U25" s="2"/>
+      <c r="V25" s="2"/>
+      <c r="W25" s="2"/>
+      <c r="X25" s="2"/>
+      <c r="Y25" s="3"/>
     </row>
     <row r="26" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B26" s="1"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="6"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="7"/>
-      <c r="O26" s="7"/>
-      <c r="P26" s="8"/>
-      <c r="Q26" s="6"/>
-      <c r="R26" s="7"/>
-      <c r="S26" s="7"/>
-      <c r="T26" s="7"/>
-      <c r="U26" s="7"/>
-      <c r="V26" s="7"/>
-      <c r="W26" s="7"/>
-      <c r="X26" s="7"/>
-      <c r="Y26" s="8"/>
+      <c r="B26" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="7">
+        <v>400</v>
+      </c>
+      <c r="H26" s="8"/>
+      <c r="I26" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="J26" s="8"/>
+      <c r="K26" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="R26" s="2"/>
+      <c r="S26" s="2"/>
+      <c r="T26" s="2"/>
+      <c r="U26" s="2"/>
+      <c r="V26" s="2"/>
+      <c r="W26" s="2"/>
+      <c r="X26" s="2"/>
+      <c r="Y26" s="3"/>
     </row>
     <row r="27" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B27" s="1"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="7"/>
-      <c r="N27" s="7"/>
-      <c r="O27" s="7"/>
-      <c r="P27" s="8"/>
-      <c r="Q27" s="6"/>
-      <c r="R27" s="7"/>
-      <c r="S27" s="7"/>
-      <c r="T27" s="7"/>
-      <c r="U27" s="7"/>
-      <c r="V27" s="7"/>
-      <c r="W27" s="7"/>
-      <c r="X27" s="7"/>
-      <c r="Y27" s="8"/>
+      <c r="B27" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="7">
+        <v>400</v>
+      </c>
+      <c r="H27" s="8"/>
+      <c r="I27" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="J27" s="8"/>
+      <c r="K27" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="R27" s="2"/>
+      <c r="S27" s="2"/>
+      <c r="T27" s="2"/>
+      <c r="U27" s="2"/>
+      <c r="V27" s="2"/>
+      <c r="W27" s="2"/>
+      <c r="X27" s="2"/>
+      <c r="Y27" s="3"/>
     </row>
     <row r="28" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="4"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="2"/>
+      <c r="T28" s="2"/>
+      <c r="U28" s="2"/>
+      <c r="V28" s="2"/>
+      <c r="W28" s="2"/>
+      <c r="X28" s="2"/>
+      <c r="Y28" s="3"/>
+    </row>
+    <row r="29" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B29" s="4"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="2"/>
+      <c r="S29" s="2"/>
+      <c r="T29" s="2"/>
+      <c r="U29" s="2"/>
+      <c r="V29" s="2"/>
+      <c r="W29" s="2"/>
+      <c r="X29" s="2"/>
+      <c r="Y29" s="3"/>
+    </row>
+    <row r="30" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B30" s="4"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="1"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="2"/>
+      <c r="T30" s="2"/>
+      <c r="U30" s="2"/>
+      <c r="V30" s="2"/>
+      <c r="W30" s="2"/>
+      <c r="X30" s="2"/>
+      <c r="Y30" s="3"/>
+    </row>
+    <row r="31" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B31" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="4">
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="7">
         <v>400</v>
       </c>
-      <c r="H28" s="5"/>
-      <c r="I28" s="4" t="s">
+      <c r="H31" s="8"/>
+      <c r="I31" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="J28" s="5"/>
-      <c r="K28" s="6" t="s">
+      <c r="J31" s="8"/>
+      <c r="K31" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7"/>
-      <c r="N28" s="7"/>
-      <c r="O28" s="7"/>
-      <c r="P28" s="8"/>
-      <c r="Q28" s="6" t="s">
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="3"/>
+      <c r="Q31" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="R28" s="7"/>
-      <c r="S28" s="7"/>
-      <c r="T28" s="7"/>
-      <c r="U28" s="7"/>
-      <c r="V28" s="7"/>
-      <c r="W28" s="7"/>
-      <c r="X28" s="7"/>
-      <c r="Y28" s="8"/>
-    </row>
-    <row r="29" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B29" s="1" t="s">
+      <c r="R31" s="2"/>
+      <c r="S31" s="2"/>
+      <c r="T31" s="2"/>
+      <c r="U31" s="2"/>
+      <c r="V31" s="2"/>
+      <c r="W31" s="2"/>
+      <c r="X31" s="2"/>
+      <c r="Y31" s="3"/>
+    </row>
+    <row r="32" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B32" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="4">
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="7">
         <v>400</v>
       </c>
-      <c r="H29" s="5"/>
-      <c r="I29" s="4" t="s">
+      <c r="H32" s="8"/>
+      <c r="I32" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="J29" s="5"/>
-      <c r="K29" s="6" t="s">
+      <c r="J32" s="8"/>
+      <c r="K32" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
-      <c r="N29" s="7"/>
-      <c r="O29" s="7"/>
-      <c r="P29" s="8"/>
-      <c r="Q29" s="6" t="s">
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="R29" s="7"/>
-      <c r="S29" s="7"/>
-      <c r="T29" s="7"/>
-      <c r="U29" s="7"/>
-      <c r="V29" s="7"/>
-      <c r="W29" s="7"/>
-      <c r="X29" s="7"/>
-      <c r="Y29" s="8"/>
-    </row>
-    <row r="30" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B30" s="1" t="s">
+      <c r="R32" s="2"/>
+      <c r="S32" s="2"/>
+      <c r="T32" s="2"/>
+      <c r="U32" s="2"/>
+      <c r="V32" s="2"/>
+      <c r="W32" s="2"/>
+      <c r="X32" s="2"/>
+      <c r="Y32" s="3"/>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B33" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="4">
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="7">
         <v>400</v>
       </c>
-      <c r="H30" s="5"/>
-      <c r="I30" s="4" t="s">
+      <c r="H33" s="8"/>
+      <c r="I33" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="J30" s="5"/>
-      <c r="K30" s="6" t="s">
+      <c r="J33" s="8"/>
+      <c r="K33" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="L30" s="7"/>
-      <c r="M30" s="7"/>
-      <c r="N30" s="7"/>
-      <c r="O30" s="7"/>
-      <c r="P30" s="8"/>
-      <c r="Q30" s="6" t="s">
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" s="3"/>
+      <c r="Q33" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="R30" s="7"/>
-      <c r="S30" s="7"/>
-      <c r="T30" s="7"/>
-      <c r="U30" s="7"/>
-      <c r="V30" s="7"/>
-      <c r="W30" s="7"/>
-      <c r="X30" s="7"/>
-      <c r="Y30" s="8"/>
-    </row>
-    <row r="31" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B31" s="1"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="5"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="7"/>
-      <c r="M31" s="7"/>
-      <c r="N31" s="7"/>
-      <c r="O31" s="7"/>
-      <c r="P31" s="8"/>
-      <c r="Q31" s="6"/>
-      <c r="R31" s="7"/>
-      <c r="S31" s="7"/>
-      <c r="T31" s="7"/>
-      <c r="U31" s="7"/>
-      <c r="V31" s="7"/>
-      <c r="W31" s="7"/>
-      <c r="X31" s="7"/>
-      <c r="Y31" s="8"/>
-    </row>
-    <row r="32" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B32" s="1"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="5"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="5"/>
-      <c r="K32" s="6"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="7"/>
-      <c r="N32" s="7"/>
-      <c r="O32" s="7"/>
-      <c r="P32" s="8"/>
-      <c r="Q32" s="6"/>
-      <c r="R32" s="7"/>
-      <c r="S32" s="7"/>
-      <c r="T32" s="7"/>
-      <c r="U32" s="7"/>
-      <c r="V32" s="7"/>
-      <c r="W32" s="7"/>
-      <c r="X32" s="7"/>
-      <c r="Y32" s="8"/>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B33" s="1"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="5"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="5"/>
-      <c r="K33" s="6"/>
-      <c r="L33" s="7"/>
-      <c r="M33" s="7"/>
-      <c r="N33" s="7"/>
-      <c r="O33" s="7"/>
-      <c r="P33" s="8"/>
-      <c r="Q33" s="6"/>
-      <c r="R33" s="7"/>
-      <c r="S33" s="7"/>
-      <c r="T33" s="7"/>
-      <c r="U33" s="7"/>
-      <c r="V33" s="7"/>
-      <c r="W33" s="7"/>
-      <c r="X33" s="7"/>
-      <c r="Y33" s="8"/>
+      <c r="R33" s="2"/>
+      <c r="S33" s="2"/>
+      <c r="T33" s="2"/>
+      <c r="U33" s="2"/>
+      <c r="V33" s="2"/>
+      <c r="W33" s="2"/>
+      <c r="X33" s="2"/>
+      <c r="Y33" s="3"/>
     </row>
     <row r="34" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B34" s="1"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="5"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="5"/>
-      <c r="K34" s="6"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="7"/>
-      <c r="N34" s="7"/>
-      <c r="O34" s="7"/>
-      <c r="P34" s="8"/>
-      <c r="Q34" s="6"/>
-      <c r="R34" s="7"/>
-      <c r="S34" s="7"/>
-      <c r="T34" s="7"/>
-      <c r="U34" s="7"/>
-      <c r="V34" s="7"/>
-      <c r="W34" s="7"/>
-      <c r="X34" s="7"/>
-      <c r="Y34" s="8"/>
+      <c r="B34" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="7">
+        <v>400</v>
+      </c>
+      <c r="H34" s="8"/>
+      <c r="I34" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="J34" s="8"/>
+      <c r="K34" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" s="3"/>
+      <c r="Q34" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="R34" s="2"/>
+      <c r="S34" s="2"/>
+      <c r="T34" s="2"/>
+      <c r="U34" s="2"/>
+      <c r="V34" s="2"/>
+      <c r="W34" s="2"/>
+      <c r="X34" s="2"/>
+      <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B35" s="1"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="5"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="5"/>
-      <c r="K35" s="6"/>
-      <c r="L35" s="7"/>
-      <c r="M35" s="7"/>
-      <c r="N35" s="7"/>
-      <c r="O35" s="7"/>
-      <c r="P35" s="8"/>
-      <c r="Q35" s="6"/>
-      <c r="R35" s="7"/>
-      <c r="S35" s="7"/>
-      <c r="T35" s="7"/>
-      <c r="U35" s="7"/>
-      <c r="V35" s="7"/>
-      <c r="W35" s="7"/>
-      <c r="X35" s="7"/>
-      <c r="Y35" s="8"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" s="3"/>
+      <c r="Q35" s="1"/>
+      <c r="R35" s="2"/>
+      <c r="S35" s="2"/>
+      <c r="T35" s="2"/>
+      <c r="U35" s="2"/>
+      <c r="V35" s="2"/>
+      <c r="W35" s="2"/>
+      <c r="X35" s="2"/>
+      <c r="Y35" s="3"/>
+    </row>
+    <row r="36" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B36" s="4"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="7"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="7"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="3"/>
+      <c r="Q36" s="1"/>
+      <c r="R36" s="2"/>
+      <c r="S36" s="2"/>
+      <c r="T36" s="2"/>
+      <c r="U36" s="2"/>
+      <c r="V36" s="2"/>
+      <c r="W36" s="2"/>
+      <c r="X36" s="2"/>
+      <c r="Y36" s="3"/>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B37" s="4"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="7"/>
+      <c r="H37" s="8"/>
+      <c r="I37" s="7"/>
+      <c r="J37" s="8"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" s="3"/>
+      <c r="Q37" s="1"/>
+      <c r="R37" s="2"/>
+      <c r="S37" s="2"/>
+      <c r="T37" s="2"/>
+      <c r="U37" s="2"/>
+      <c r="V37" s="2"/>
+      <c r="W37" s="2"/>
+      <c r="X37" s="2"/>
+      <c r="Y37" s="3"/>
+    </row>
+    <row r="38" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B38" s="4"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="7"/>
+      <c r="J38" s="8"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" s="3"/>
+      <c r="Q38" s="1"/>
+      <c r="R38" s="2"/>
+      <c r="S38" s="2"/>
+      <c r="T38" s="2"/>
+      <c r="U38" s="2"/>
+      <c r="V38" s="2"/>
+      <c r="W38" s="2"/>
+      <c r="X38" s="2"/>
+      <c r="Y38" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="151">
+  <mergeCells count="166">
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B2:Y4"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B33:F33"/>
     <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="B2:Y4"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B8:F8"/>
@@ -1626,58 +1793,49 @@
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B35:F35"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B18:F18"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="K38:P38"/>
+    <mergeCell ref="K31:P31"/>
+    <mergeCell ref="Q31:Y31"/>
+    <mergeCell ref="Q38:Y38"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="K36:P36"/>
+    <mergeCell ref="Q36:Y36"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="K37:P37"/>
+    <mergeCell ref="Q37:Y37"/>
+    <mergeCell ref="Q12:Y12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="K34:P34"/>
+    <mergeCell ref="Q34:Y34"/>
     <mergeCell ref="G35:H35"/>
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="K35:P35"/>
     <mergeCell ref="Q35:Y35"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="K32:P32"/>
+    <mergeCell ref="Q32:Y32"/>
     <mergeCell ref="G33:H33"/>
     <mergeCell ref="I33:J33"/>
     <mergeCell ref="K33:P33"/>
     <mergeCell ref="Q33:Y33"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="K34:P34"/>
-    <mergeCell ref="Q34:Y34"/>
-    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="G32:H32"/>
     <mergeCell ref="G31:H31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="K31:P31"/>
-    <mergeCell ref="Q31:Y31"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="K32:P32"/>
-    <mergeCell ref="Q32:Y32"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="K29:P29"/>
-    <mergeCell ref="Q29:Y29"/>
-    <mergeCell ref="G30:H30"/>
     <mergeCell ref="I30:J30"/>
     <mergeCell ref="K30:P30"/>
     <mergeCell ref="Q30:Y30"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="Q13:Y13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="K14:P14"/>
-    <mergeCell ref="Q14:Y14"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:P17"/>
-    <mergeCell ref="Q17:Y17"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:P12"/>
-    <mergeCell ref="Q12:Y12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="K18:P18"/>
-    <mergeCell ref="Q18:Y18"/>
+    <mergeCell ref="I31:J31"/>
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="G9:H9"/>
@@ -1690,13 +1848,18 @@
     <mergeCell ref="K11:P11"/>
     <mergeCell ref="Q11:Y11"/>
     <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="K27:P27"/>
-    <mergeCell ref="Q27:Y27"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="K28:P28"/>
-    <mergeCell ref="Q28:Y28"/>
     <mergeCell ref="K13:P13"/>
+    <mergeCell ref="Q13:Y13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="K14:P14"/>
+    <mergeCell ref="Q14:Y14"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:P17"/>
+    <mergeCell ref="Q17:Y17"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:P12"/>
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="G10:H10"/>
     <mergeCell ref="I8:J8"/>
@@ -1726,21 +1889,34 @@
     <mergeCell ref="I16:J16"/>
     <mergeCell ref="K16:P16"/>
     <mergeCell ref="Q16:Y16"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="K18:P18"/>
+    <mergeCell ref="Q18:Y18"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="K29:P29"/>
+    <mergeCell ref="Q29:Y29"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="K24:P24"/>
+    <mergeCell ref="Q24:Y24"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="K28:P28"/>
+    <mergeCell ref="Q28:Y28"/>
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="G26:H26"/>
     <mergeCell ref="I26:J26"/>
     <mergeCell ref="K26:P26"/>
     <mergeCell ref="Q26:Y26"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="K24:P24"/>
-    <mergeCell ref="Q24:Y24"/>
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="G25:H25"/>
     <mergeCell ref="I25:J25"/>
     <mergeCell ref="K25:P25"/>
-    <mergeCell ref="Q25:Y25"/>
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="G20:H20"/>
     <mergeCell ref="I20:J20"/>
@@ -1751,6 +1927,12 @@
     <mergeCell ref="I21:J21"/>
     <mergeCell ref="K21:P21"/>
     <mergeCell ref="Q21:Y21"/>
+    <mergeCell ref="Q25:Y25"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="K27:P27"/>
+    <mergeCell ref="Q27:Y27"/>
     <mergeCell ref="B22:F22"/>
     <mergeCell ref="G22:H22"/>
     <mergeCell ref="I22:J22"/>
